--- a/劉怡伶/HW1011/HW 1011 v1.xlsx
+++ b/劉怡伶/HW1011/HW 1011 v1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b9361\Desktop\在職\統計學\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5264A7-4CFB-4174-A9D4-02D7052BE754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBC4AD6-CA3C-43FC-B541-2ECF20029E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FAF24491-FACC-47A3-91A1-021646E0C0B6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
   <si>
     <t>a.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,61 +224,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>P(u-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="161"/>
-      </rPr>
-      <t>σ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;x&lt;u+2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-      </rPr>
-      <t>σ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(3.55&lt;x&lt;12.25)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>u-2</t>
-    </r>
+    <t>CH05.02_44</t>
+  </si>
+  <si>
+    <t>n=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p=0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -303,9 +263,145 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Z=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH05.02_47</t>
+  </si>
+  <si>
+    <t>47. 植物遺傳學</t>
+  </si>
+  <si>
     <r>
-      <t>u+2</t>
+      <t>(b)</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 計算 P(x≥9)P(x \geq 9)P(x≥9)。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(c)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 計算 P(x≤1)P(x \leq 1)P(x≤1)。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(d)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 如果觀察到只有一株植物有紅色花瓣，其餘九株植物都是條紋花瓣，這是否不尋常？若這些實驗結果確實發生了，你可以得出什麼結論？</t>
+    </r>
+  </si>
+  <si>
+    <t>n=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紅花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一株具有紅色花瓣的牡丹植物與一株具有條紋花瓣的牡丹植物交配。來自這次交配的後代有紅色花的機率為 0.75。令 x 為從這次交配所得的 10 顆種子中長出紅色花瓣植物的數量。這些種子都已被收集並發芽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 隨機變數 x 是否服從二項分配？如果不服從，為什麼？如果服從，n 和 p 的值為何？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YES,只有紅和非紅兩種結果, n=10 , p=0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(x&lt;=9)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(x&lt;=1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>--&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outlier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH06.02_51</t>
+  </si>
+  <si>
+    <t>No.it is not unusual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH06.02_59</t>
+  </si>
+  <si>
+    <t>Yes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH06.03_17</t>
+  </si>
+  <si>
+    <t>CH06.03_20</t>
+  </si>
+  <si>
+    <t>p=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -320,286 +416,123 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="新細明體"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
       </rPr>
       <t>=</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CH05.02_44</t>
-  </si>
-  <si>
-    <t>=0.9973-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=0.9745</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>n=10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p=0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-      </rPr>
-      <t>σ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(X&gt;6)=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(Z&gt;0.63)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z=</t>
-  </si>
-  <si>
-    <t>Z=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(4&lt;X&lt;6)=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(-0.63&lt;Z&lt;0.63)=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CH05.02_47</t>
-  </si>
-  <si>
-    <t>47. 植物遺傳學</t>
-  </si>
-  <si>
-    <r>
-      <t>(b)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 計算 P(x≥9)P(x \geq 9)P(x≥9)。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>(c)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 計算 P(x≤1)P(x \leq 1)P(x≤1)。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>(d)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 如果觀察到只有一株植物有紅色花瓣，其餘九株植物都是條紋花瓣，這是否不尋常？若這些實驗結果確實發生了，你可以得出什麼結論？</t>
-    </r>
-  </si>
-  <si>
-    <t>n=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>紅花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一株具有紅色花瓣的牡丹植物與一株具有條紋花瓣的牡丹植物交配。來自這次交配的後代有紅色花的機率為 0.75。令 x 為從這次交配所得的 10 顆種子中長出紅色花瓣植物的數量。這些種子都已被收集並發芽。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(a)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 隨機變數 x 是否服從二項分配？如果不服從，為什麼？如果服從，n 和 p 的值為何？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YES,只有紅和非紅兩種結果, n=10 , p=0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(x&lt;=9)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(x&gt;=9)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(x&lt;=1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>--&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>outlier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CH06.02_51</t>
-  </si>
-  <si>
-    <t>No.it is not unusual</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CH06.02_59</t>
-  </si>
-  <si>
-    <r>
-      <t>u+3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-      </rPr>
-      <t>σ</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>u-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-      </rPr>
-      <t>σ</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>180 &lt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CH06.03_17</t>
-  </si>
-  <si>
-    <t>CH06.03_20</t>
-  </si>
-  <si>
-    <t>p=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(X&gt;=55)=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=1-0.7881=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P(Z&gt;0.8)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=1-0.758</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Not a raw event</t>
+    <t>p(4&lt;=x&lt;=12)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=1-0.828</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(4&lt;=y&lt;=6)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(4&lt;=x&lt;=6)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(x&gt;6)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.828-0.172=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=1-0.7375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(x&gt;=9)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-P(x&lt;=8)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=(188-176.5)/8.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(x=0.25)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(x=0.75)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X=u+zQ=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(Q1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(Q3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>np</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(X&gt;=59.5)=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(Z&gt;1.7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=1-0.9554=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=1-0.9009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(X&gt;=59.5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p(x)&lt;=5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rare event</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9% --&gt; not rare</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -646,13 +579,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="161"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <charset val="161"/>
     </font>
@@ -672,6 +598,12 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -731,7 +663,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -771,14 +703,20 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2797,856 +2735,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="直線接點 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC506806-933A-4F66-AC33-90E5A3788354}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7251700" y="425450"/>
-          <a:ext cx="660400" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="直線接點 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDA10046-4FB5-459E-99D7-46615E1F1E64}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7226300" y="742950"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="64" name="直線接點 63">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56CFBD63-EB6B-4599-BE5F-C968C4979DD7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8667750" y="349250"/>
-          <a:ext cx="260350" cy="6350"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="67" name="直線接點 66">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBAE9F43-7A8A-446B-B4DB-BC88B18AD6BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8667750" y="996950"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="73" name="直線接點 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED9E8D54-E4CC-4802-8C4B-07D4E500E589}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7302500" y="1339850"/>
-          <a:ext cx="571500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>565150</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="74" name="直線接點 73">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4105700D-A474-4B2B-8025-18CB9E885D9A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7277100" y="1543050"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="77" name="直線接點 76">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1137E9C4-F63E-4EE2-90AD-DB7DC5A8E479}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8686800" y="1447800"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="78" name="直線接點 77">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77F2E628-EF55-47D7-9652-500360952F6C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8693150" y="1847850"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="80" name="直線接點 79">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{855D1BD4-1485-4B63-AD44-2A8BF74363D6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7315200" y="2254250"/>
-          <a:ext cx="571500" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>577850</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="81" name="直線接點 80">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{487FA7E9-3F20-4C06-BB79-078262F79108}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7289800" y="2457450"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="82" name="直線接點 81">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29BE81DC-F105-4957-B268-7857415FEA72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8705850" y="2279650"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="83" name="直線接點 82">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA36F0A4-B751-4AA6-9D63-87410E3106F5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8731250" y="2705100"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="100" name="直線接點 99">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16D23652-C56F-465F-BD92-0EE4B260A838}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7086600" y="546100"/>
-          <a:ext cx="749300" cy="336550"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="105" name="直線接點 104">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F354C45-DB29-4486-94E8-3DFD5BE1474C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7080250" y="876300"/>
-          <a:ext cx="781050" cy="1136650"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="117" name="直線接點 116">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73A7DFA9-278C-4864-B980-6925EA7CD52C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8445500" y="527050"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="118" name="直線接點 117">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2D5F099-21A5-47CC-BAB3-AB90A2167B51}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="9886950" y="133350"/>
-          <a:ext cx="260350" cy="6350"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="119" name="直線接點 118">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6C824A4-9331-4F02-AC2C-7D8FF1E20F8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9886950" y="781050"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
       <xdr:colOff>596900</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
@@ -3747,56 +2835,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="122" name="直線接點 121">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E951F52-E340-4BC3-B639-BD019740C02A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9906000" y="1231900"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
@@ -3947,56 +2985,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="126" name="直線接點 125">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EB2019B-1313-41FB-BF07-FC2FFCE99A5B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9925050" y="2063750"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
       <xdr:colOff>196850</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -4297,206 +3285,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="140" name="直線接點 139">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B800DF-66A0-4C9D-9C51-12F6277708C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8470900" y="209550"/>
-          <a:ext cx="660400" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="141" name="直線接點 140">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CCF9942-79FA-4EEB-B31C-BA49351F3682}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8445500" y="527050"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="142" name="直線接點 141">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5E45B14-F503-41CD-87A5-57AC758BC055}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="9886950" y="133350"/>
-          <a:ext cx="260350" cy="6350"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="143" name="直線接點 142">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A59683-1C1A-40F1-92B1-CBB6B7530341}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9886950" y="781050"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
       <xdr:colOff>596900</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
@@ -4597,56 +3385,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="146" name="直線接點 145">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1415CCBA-1A5F-4D0C-9828-2CD58F466FBE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9906000" y="1231900"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
@@ -4797,56 +3535,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="150" name="直線接點 149">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3946ABD2-493D-444E-8E9D-41844D1F5890}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9925050" y="2063750"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
       <xdr:colOff>196850</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -5047,56 +3735,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="155" name="直線接點 154">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9E0FC71-2A8D-4685-92CF-BF597E854164}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8470900" y="3232150"/>
-          <a:ext cx="660400" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
       <xdr:colOff>520700</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -5122,106 +3760,6 @@
         <a:xfrm>
           <a:off x="8445500" y="3549650"/>
           <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="157" name="直線接點 156">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10C954D1-9292-4C12-88F4-437A8A418219}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="9886950" y="3155950"/>
-          <a:ext cx="260350" cy="6350"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="158" name="直線接點 157">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{487D3397-360E-48DF-81E6-4DBE9E3E4FB3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9886950" y="3803650"/>
-          <a:ext cx="298450" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5347,56 +3885,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="161" name="直線接點 160">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2073EC9D-1DC8-42AF-80EB-53A58D1646C0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9906000" y="4254500"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
@@ -5547,56 +4035,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="165" name="直線接點 164">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2DD9FFC-F23C-4828-A0AA-47A11EB322AD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9925050" y="5086350"/>
-          <a:ext cx="298450" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
       <xdr:colOff>196850</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -5772,156 +4210,6 @@
         <a:xfrm>
           <a:off x="7080250" y="3898900"/>
           <a:ext cx="781050" cy="1136650"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="177" name="直線接點 176">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783F1051-8619-4576-9D51-F1B7835BCD6F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8445500" y="3549650"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="178" name="直線接點 177">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF8B3727-745C-45A9-8B6C-94DB6BF53790}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8445500" y="3549650"/>
-          <a:ext cx="603250" cy="222250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="180" name="直線接點 179">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07950796-C9A6-42DB-904D-2638A162031C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="9886950" y="133350"/>
-          <a:ext cx="260350" cy="6350"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -6112,8 +4400,8 @@
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>519122</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>423872</xdr:colOff>
       <xdr:row>130</xdr:row>
       <xdr:rowOff>45070</xdr:rowOff>
     </xdr:to>
@@ -6644,12 +4932,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3713B1-4D33-4462-B0EA-DA157747CA37}">
-  <dimension ref="A1:AD192"/>
+  <dimension ref="A1:AD191"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="8" max="8" width="11.26953125" customWidth="1"/>
     <col min="9" max="10" width="11.90625" customWidth="1"/>
+    <col min="11" max="11" width="16.6328125" customWidth="1"/>
     <col min="12" max="12" width="7.36328125" customWidth="1"/>
+    <col min="13" max="13" width="10.90625" customWidth="1"/>
     <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="8.7265625" customWidth="1"/>
     <col min="20" max="20" width="9.1796875" bestFit="1" customWidth="1"/>
@@ -6932,27 +5222,33 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="L35" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I47" t="s">
         <v>0</v>
       </c>
-      <c r="J47">
+      <c r="J47" t="s">
+        <v>50</v>
+      </c>
+      <c r="K47">
         <v>7.9</v>
       </c>
       <c r="N47" t="s">
         <v>1</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P47">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -7004,10 +5300,7 @@
       <c r="N51" t="s">
         <v>2</v>
       </c>
-      <c r="O51" s="2">
-        <f>P56</f>
-        <v>0.97399425268372619</v>
-      </c>
+      <c r="O51" s="2"/>
     </row>
     <row r="52" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I52">
@@ -7025,7 +5318,11 @@
         <v>0.58870000000000022</v>
       </c>
       <c r="N52" t="s">
-        <v>47</v>
+        <v>77</v>
+      </c>
+      <c r="P52">
+        <f>SUM(J51:J59)</f>
+        <v>0.96</v>
       </c>
     </row>
     <row r="53" spans="9:17" x14ac:dyDescent="0.4">
@@ -7043,13 +5340,6 @@
         <f t="shared" si="1"/>
         <v>0.36100000000000015</v>
       </c>
-      <c r="N53" t="s">
-        <v>48</v>
-      </c>
-      <c r="P53">
-        <f>SUM(J51:J59)</f>
-        <v>0.96</v>
-      </c>
     </row>
     <row r="54" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I54">
@@ -7066,17 +5356,6 @@
         <f t="shared" si="1"/>
         <v>0.1134000000000001</v>
       </c>
-      <c r="N54" t="s">
-        <v>49</v>
-      </c>
-      <c r="O54">
-        <f>K61-2*L62</f>
-        <v>3.5502873658136913</v>
-      </c>
-      <c r="P54">
-        <f>(J51-J50)*(4-O54)</f>
-        <v>8.9942526837261758E-3</v>
-      </c>
     </row>
     <row r="55" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I55">
@@ -7093,17 +5372,6 @@
         <f t="shared" si="1"/>
         <v>1.9999999999999857E-3</v>
       </c>
-      <c r="N55" t="s">
-        <v>50</v>
-      </c>
-      <c r="O55">
-        <f>K61+2*L62</f>
-        <v>12.249712634186309</v>
-      </c>
-      <c r="P55">
-        <f>(J59-J60)*0.25</f>
-        <v>4.9999999999999992E-3</v>
-      </c>
     </row>
     <row r="56" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I56">
@@ -7120,10 +5388,6 @@
         <f t="shared" si="1"/>
         <v>0.21779999999999985</v>
       </c>
-      <c r="P56">
-        <f>SUM(P53:P55)</f>
-        <v>0.97399425268372619</v>
-      </c>
     </row>
     <row r="57" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I57">
@@ -7140,18 +5404,8 @@
         <f t="shared" si="1"/>
         <v>0.52919999999999978</v>
       </c>
-      <c r="N57" t="s">
-        <v>54</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P57">
-        <v>2.2800000000000001E-2</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="O57" s="1"/>
+      <c r="Q57" s="1"/>
     </row>
     <row r="58" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I58">
@@ -7219,22 +5473,22 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.4">
       <c r="I77" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.4">
       <c r="I78" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.4">
       <c r="I79" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J79">
         <f>10*0.5</f>
@@ -7243,7 +5497,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.4">
       <c r="I80" s="13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J80" s="3">
         <f>SQRT(J79*0.5)</f>
@@ -7254,24 +5508,17 @@
       <c r="I81" t="s">
         <v>0</v>
       </c>
-      <c r="J81" t="s">
-        <v>62</v>
-      </c>
-      <c r="K81">
-        <f>(6-J79)/J80</f>
-        <v>0.63245553203367588</v>
-      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I82" t="s">
-        <v>59</v>
-      </c>
-      <c r="J82" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="K82" s="10">
-        <f>1-0.7357</f>
-        <v>0.26429999999999998</v>
+        <f>1-0.828</f>
+        <v>0.17200000000000004</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.4">
@@ -7281,83 +5528,77 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I85" t="s">
-        <v>61</v>
-      </c>
-      <c r="J85">
-        <v>0.63245553203367588</v>
+        <v>80</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="K85">
-        <f>(4-J79)/J80</f>
-        <v>-0.63245553203367588</v>
+        <f>0.828-0.172</f>
+        <v>0.65599999999999992</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I87" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I88" t="s">
-        <v>64</v>
+        <v>79</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="K88">
-        <f>1-K82*2</f>
-        <v>0.47140000000000004</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="I90" t="s">
-        <v>2</v>
-      </c>
-      <c r="J90">
-        <f>K88</f>
-        <v>0.47140000000000004</v>
+        <f>0.828-0.172</f>
+        <v>0.65599999999999992</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A92" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I95" s="14" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I96" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="9:14" x14ac:dyDescent="0.4">
       <c r="I98" s="14" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="9:14" x14ac:dyDescent="0.4">
       <c r="I99" s="14" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="9:14" x14ac:dyDescent="0.4">
       <c r="I100" s="14" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="9:14" x14ac:dyDescent="0.4">
       <c r="I101" s="14" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103" spans="9:14" x14ac:dyDescent="0.4">
       <c r="I103" s="14" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J103">
         <v>10</v>
       </c>
       <c r="L103" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M103">
         <f>J103*J104</f>
@@ -7366,16 +5607,16 @@
     </row>
     <row r="104" spans="9:14" x14ac:dyDescent="0.4">
       <c r="I104" s="14" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="J104">
         <v>0.75</v>
       </c>
       <c r="K104" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="L104" s="13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M104" s="3">
         <f>SQRT(M103*0.25)</f>
@@ -7387,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106" spans="9:14" x14ac:dyDescent="0.4">
@@ -7395,27 +5636,33 @@
         <v>1</v>
       </c>
       <c r="J106">
-        <v>0.97199999999999998</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="K106">
-        <v>0.89300000000000002</v>
+        <v>0.624</v>
       </c>
       <c r="L106" s="10">
         <f>(J106+K106)/2</f>
-        <v>0.9325</v>
+        <v>0.73750000000000004</v>
       </c>
       <c r="M106" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="9:14" x14ac:dyDescent="0.4">
+      <c r="I107" t="s">
+        <v>84</v>
+      </c>
       <c r="J107" t="s">
-        <v>77</v>
-      </c>
-      <c r="K107">
+        <v>85</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L107">
         <f>1-L106</f>
-        <v>6.7500000000000004E-2</v>
+        <v>0.26249999999999996</v>
       </c>
       <c r="N107" s="14"/>
     </row>
@@ -7424,10 +5671,10 @@
         <v>2</v>
       </c>
       <c r="J108" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="9:14" x14ac:dyDescent="0.4">
@@ -7435,138 +5682,181 @@
         <v>3</v>
       </c>
       <c r="J109" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K109">
         <f>(1-M103)/M104</f>
         <v>-4.7469288317114398</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="M109" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
       <c r="J136" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K136">
         <v>176.5</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
       <c r="J137" s="13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K137">
         <v>8.9</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
       <c r="J139" t="s">
-        <v>62</v>
-      </c>
-      <c r="K139">
-        <f>(188-K136)/K137</f>
+        <v>52</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L139">
         <v>1.2921348314606742</v>
       </c>
-      <c r="L139" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M139" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
       <c r="K140" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K143" s="1"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A148" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.4">
       <c r="J151" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K151">
         <v>278</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.4">
       <c r="J152" s="13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K152">
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.4">
       <c r="J154" t="s">
         <v>0</v>
       </c>
-      <c r="K154">
-        <f>K151+3*K152</f>
-        <v>314</v>
+      <c r="K154" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="L154" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="K155">
-        <f>K151-3*K152</f>
-        <v>242</v>
+        <v>92</v>
+      </c>
+      <c r="M154" t="s">
+        <v>88</v>
+      </c>
+      <c r="N154">
+        <v>-0.67500000000000004</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="K155" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="L155" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="J157" t="s">
+        <v>92</v>
+      </c>
+      <c r="M155" t="s">
+        <v>89</v>
+      </c>
+      <c r="N155">
+        <v>0.67500000000000004</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="K156" t="s">
+        <v>93</v>
+      </c>
+      <c r="L156" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M156" t="s">
+        <v>92</v>
+      </c>
+      <c r="N156">
+        <f>K151+N154*K152</f>
+        <v>269.89999999999998</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="L157" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="M157" t="s">
+        <v>92</v>
+      </c>
+      <c r="N157">
+        <f>K151+K152*N155</f>
+        <v>286.10000000000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="J159" t="s">
         <v>1</v>
       </c>
-      <c r="K157" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="K158" t="s">
-        <v>88</v>
-      </c>
-      <c r="L158">
-        <v>242</v>
+      <c r="K159" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="K160" t="s">
+        <v>52</v>
+      </c>
+      <c r="L160">
+        <f>(180-K151)/K152</f>
+        <v>-8.1666666666666661</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A162" s="4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H164" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I164" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J164" s="15" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K164" s="10">
-        <f>1-0.7881</f>
-        <v>0.21189999999999998</v>
+        <f>1-0.9554</f>
+        <v>4.4599999999999973E-2</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H165" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I165">
         <v>100</v>
@@ -7574,7 +5864,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H166" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I166">
         <v>0.51</v>
@@ -7582,7 +5872,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H167" s="13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I167">
         <f>SQRT(I165*I166*(1-I166))</f>
@@ -7591,101 +5881,103 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H168" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I168">
         <f>I165*I166</f>
         <v>51</v>
       </c>
+      <c r="J168" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H169" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="I169">
-        <f>(55-51)/I167</f>
-        <v>0.8001600480160056</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.4">
+        <f>(59.5-51)/I167</f>
+        <v>1.7003401020340119</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A182" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I183" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I184" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="J184">
         <f>1/1000</f>
         <v>1E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I185" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J185">
         <v>50000</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I186" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J186">
         <f>J184*J185</f>
         <v>50</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I187" s="13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J187">
         <f>SQRT(J185*J184*(1-J184))</f>
         <v>7.067531393633848</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I188" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K188" s="10">
-        <v>0.24199999999999999</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.4">
+        <f>1-0.9009</f>
+        <v>9.9099999999999966E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I189" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="J189">
-        <f>(55-J186)/J187</f>
-        <v>0.70746059996334809</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.4">
+        <f>(59.5-J186)/J187</f>
+        <v>1.3441751399303614</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.4">
       <c r="I191" t="s">
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>61</v>
-      </c>
-      <c r="K191">
-        <v>0.70746059996334809</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="J192" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="K191" t="s">
+        <v>103</v>
+      </c>
+      <c r="L191" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
